--- a/Elthaghr_result.xlsx
+++ b/Elthaghr_result.xlsx
@@ -2610,10 +2610,10 @@
     <t>رئيس الكنترول</t>
   </si>
   <si>
-    <t>مديرة القسم الااعدادي</t>
-  </si>
-  <si>
     <t>أ / عبير عبدالله</t>
+  </si>
+  <si>
+    <t>مديرة القسم الاعدادي</t>
   </si>
 </sst>
 </file>
@@ -3107,7 +3107,7 @@
         <v>861</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>855</v>
@@ -3169,7 +3169,7 @@
         <v>856</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>857</v>
@@ -3231,7 +3231,7 @@
         <v>856</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T3" s="2" t="s">
         <v>857</v>
@@ -3293,7 +3293,7 @@
         <v>856</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T4" s="2" t="s">
         <v>857</v>
@@ -3355,7 +3355,7 @@
         <v>856</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T5" s="2" t="s">
         <v>857</v>
@@ -3417,7 +3417,7 @@
         <v>856</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T6" s="2" t="s">
         <v>857</v>
@@ -3479,7 +3479,7 @@
         <v>856</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>857</v>
@@ -3541,7 +3541,7 @@
         <v>856</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T8" s="2" t="s">
         <v>857</v>
@@ -3603,7 +3603,7 @@
         <v>856</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T9" s="2" t="s">
         <v>857</v>
@@ -3665,7 +3665,7 @@
         <v>856</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T10" s="2" t="s">
         <v>857</v>
@@ -3727,7 +3727,7 @@
         <v>856</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T11" s="2" t="s">
         <v>857</v>
@@ -3789,7 +3789,7 @@
         <v>856</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T12" s="2" t="s">
         <v>857</v>
@@ -3851,7 +3851,7 @@
         <v>856</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T13" s="2" t="s">
         <v>857</v>
@@ -3913,7 +3913,7 @@
         <v>856</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>857</v>
@@ -3975,7 +3975,7 @@
         <v>856</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>857</v>
@@ -4037,7 +4037,7 @@
         <v>856</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>857</v>
@@ -4099,7 +4099,7 @@
         <v>856</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>857</v>
@@ -4161,7 +4161,7 @@
         <v>856</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T18" s="2" t="s">
         <v>857</v>
@@ -4223,7 +4223,7 @@
         <v>856</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>857</v>
@@ -4285,7 +4285,7 @@
         <v>856</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>857</v>
@@ -4347,7 +4347,7 @@
         <v>856</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>857</v>
@@ -4409,7 +4409,7 @@
         <v>856</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>857</v>
@@ -4471,7 +4471,7 @@
         <v>856</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>857</v>
@@ -4533,7 +4533,7 @@
         <v>856</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>857</v>
@@ -4595,7 +4595,7 @@
         <v>856</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T25" s="2" t="s">
         <v>857</v>
@@ -4657,7 +4657,7 @@
         <v>856</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T26" s="2" t="s">
         <v>857</v>
@@ -4719,7 +4719,7 @@
         <v>856</v>
       </c>
       <c r="S27" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>857</v>
@@ -4781,7 +4781,7 @@
         <v>856</v>
       </c>
       <c r="S28" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>857</v>
@@ -4843,7 +4843,7 @@
         <v>856</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>857</v>
@@ -4905,7 +4905,7 @@
         <v>856</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>857</v>
@@ -4967,7 +4967,7 @@
         <v>856</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>857</v>
@@ -5029,7 +5029,7 @@
         <v>856</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>857</v>
@@ -5091,7 +5091,7 @@
         <v>856</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>857</v>
@@ -5153,7 +5153,7 @@
         <v>856</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>857</v>
@@ -5215,7 +5215,7 @@
         <v>856</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>857</v>
@@ -5277,7 +5277,7 @@
         <v>856</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T36" s="2" t="s">
         <v>857</v>
@@ -5339,7 +5339,7 @@
         <v>856</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>857</v>
@@ -5401,7 +5401,7 @@
         <v>856</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>857</v>
@@ -5463,7 +5463,7 @@
         <v>856</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>857</v>
@@ -5525,7 +5525,7 @@
         <v>856</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>857</v>
@@ -5587,7 +5587,7 @@
         <v>856</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>857</v>
@@ -5649,7 +5649,7 @@
         <v>856</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>857</v>
@@ -5711,7 +5711,7 @@
         <v>856</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T43" s="2" t="s">
         <v>857</v>
@@ -5773,7 +5773,7 @@
         <v>856</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T44" s="2" t="s">
         <v>857</v>
@@ -5835,7 +5835,7 @@
         <v>856</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>857</v>
@@ -5897,7 +5897,7 @@
         <v>856</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>857</v>
@@ -5959,7 +5959,7 @@
         <v>856</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>857</v>
@@ -6021,7 +6021,7 @@
         <v>856</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T48" s="2" t="s">
         <v>857</v>
@@ -6083,7 +6083,7 @@
         <v>856</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>857</v>
@@ -6145,7 +6145,7 @@
         <v>856</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>857</v>
@@ -6207,7 +6207,7 @@
         <v>856</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>857</v>
@@ -6269,7 +6269,7 @@
         <v>856</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>857</v>
@@ -6331,7 +6331,7 @@
         <v>856</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>857</v>
@@ -6393,7 +6393,7 @@
         <v>856</v>
       </c>
       <c r="S54" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T54" s="2" t="s">
         <v>857</v>
@@ -6455,7 +6455,7 @@
         <v>856</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>857</v>
@@ -6517,7 +6517,7 @@
         <v>856</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>857</v>
@@ -6579,7 +6579,7 @@
         <v>856</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>857</v>
@@ -6641,7 +6641,7 @@
         <v>856</v>
       </c>
       <c r="S58" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T58" s="2" t="s">
         <v>857</v>
@@ -6703,7 +6703,7 @@
         <v>856</v>
       </c>
       <c r="S59" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>857</v>
@@ -6765,7 +6765,7 @@
         <v>856</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T60" s="2" t="s">
         <v>857</v>
@@ -6827,7 +6827,7 @@
         <v>856</v>
       </c>
       <c r="S61" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T61" s="2" t="s">
         <v>857</v>
@@ -6889,7 +6889,7 @@
         <v>856</v>
       </c>
       <c r="S62" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T62" s="2" t="s">
         <v>857</v>
@@ -6951,7 +6951,7 @@
         <v>856</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T63" s="2" t="s">
         <v>857</v>
@@ -7013,7 +7013,7 @@
         <v>856</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T64" s="2" t="s">
         <v>857</v>
@@ -7075,7 +7075,7 @@
         <v>856</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>857</v>
@@ -7137,7 +7137,7 @@
         <v>856</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T66" s="2" t="s">
         <v>857</v>
@@ -7199,7 +7199,7 @@
         <v>856</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>857</v>
@@ -7261,7 +7261,7 @@
         <v>856</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>857</v>
@@ -7323,7 +7323,7 @@
         <v>856</v>
       </c>
       <c r="S69" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>857</v>
@@ -7385,7 +7385,7 @@
         <v>856</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>857</v>
@@ -7447,7 +7447,7 @@
         <v>856</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>857</v>
@@ -7509,7 +7509,7 @@
         <v>856</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T72" s="2" t="s">
         <v>857</v>
@@ -7571,7 +7571,7 @@
         <v>856</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T73" s="2" t="s">
         <v>857</v>
@@ -7633,7 +7633,7 @@
         <v>856</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T74" s="2" t="s">
         <v>857</v>
@@ -7695,7 +7695,7 @@
         <v>856</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>857</v>
@@ -7757,7 +7757,7 @@
         <v>856</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T76" s="2" t="s">
         <v>857</v>
@@ -7819,7 +7819,7 @@
         <v>856</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T77" s="2" t="s">
         <v>857</v>
@@ -7881,7 +7881,7 @@
         <v>856</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T78" s="2" t="s">
         <v>857</v>
@@ -7943,7 +7943,7 @@
         <v>856</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T79" s="2" t="s">
         <v>857</v>
@@ -8005,7 +8005,7 @@
         <v>856</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>857</v>
@@ -8067,7 +8067,7 @@
         <v>856</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T81" s="2" t="s">
         <v>857</v>
@@ -8129,7 +8129,7 @@
         <v>856</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T82" s="2" t="s">
         <v>857</v>
@@ -8191,7 +8191,7 @@
         <v>856</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T83" s="2" t="s">
         <v>857</v>
@@ -8253,7 +8253,7 @@
         <v>856</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T84" s="2" t="s">
         <v>857</v>
@@ -8315,7 +8315,7 @@
         <v>856</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T85" s="2" t="s">
         <v>857</v>
@@ -8377,7 +8377,7 @@
         <v>856</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T86" s="2" t="s">
         <v>857</v>
@@ -8439,7 +8439,7 @@
         <v>856</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T87" s="2" t="s">
         <v>857</v>
@@ -8501,7 +8501,7 @@
         <v>856</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T88" s="2" t="s">
         <v>857</v>
@@ -8563,7 +8563,7 @@
         <v>856</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T89" s="2" t="s">
         <v>857</v>
@@ -8625,7 +8625,7 @@
         <v>856</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T90" s="2" t="s">
         <v>857</v>
@@ -8687,7 +8687,7 @@
         <v>856</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T91" s="2" t="s">
         <v>857</v>
@@ -8749,7 +8749,7 @@
         <v>856</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T92" s="2" t="s">
         <v>857</v>
@@ -8811,7 +8811,7 @@
         <v>856</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T93" s="2" t="s">
         <v>857</v>
@@ -8873,7 +8873,7 @@
         <v>856</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T94" s="2" t="s">
         <v>857</v>
@@ -8935,7 +8935,7 @@
         <v>856</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T95" s="2" t="s">
         <v>857</v>
@@ -8997,7 +8997,7 @@
         <v>856</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T96" s="2" t="s">
         <v>857</v>
@@ -9059,7 +9059,7 @@
         <v>856</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T97" s="2" t="s">
         <v>857</v>
@@ -9121,7 +9121,7 @@
         <v>856</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T98" s="2" t="s">
         <v>857</v>
@@ -9183,7 +9183,7 @@
         <v>856</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T99" s="2" t="s">
         <v>857</v>
@@ -9245,7 +9245,7 @@
         <v>856</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T100" s="2" t="s">
         <v>857</v>
@@ -9307,7 +9307,7 @@
         <v>856</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T101" s="2" t="s">
         <v>857</v>
@@ -9369,7 +9369,7 @@
         <v>856</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T102" s="2" t="s">
         <v>857</v>
@@ -9431,7 +9431,7 @@
         <v>856</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T103" s="2" t="s">
         <v>857</v>
@@ -9493,7 +9493,7 @@
         <v>856</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T104" s="2" t="s">
         <v>857</v>
@@ -9555,7 +9555,7 @@
         <v>856</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T105" s="2" t="s">
         <v>857</v>
@@ -9617,7 +9617,7 @@
         <v>856</v>
       </c>
       <c r="S106" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T106" s="2" t="s">
         <v>857</v>
@@ -9679,7 +9679,7 @@
         <v>856</v>
       </c>
       <c r="S107" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T107" s="2" t="s">
         <v>857</v>
@@ -9741,7 +9741,7 @@
         <v>856</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T108" s="2" t="s">
         <v>857</v>
@@ -9803,7 +9803,7 @@
         <v>856</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T109" s="2" t="s">
         <v>857</v>
@@ -9865,7 +9865,7 @@
         <v>856</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T110" s="2" t="s">
         <v>857</v>
@@ -9927,7 +9927,7 @@
         <v>856</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T111" s="2" t="s">
         <v>857</v>
@@ -9989,7 +9989,7 @@
         <v>856</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T112" s="2" t="s">
         <v>857</v>
@@ -10051,7 +10051,7 @@
         <v>856</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T113" s="2" t="s">
         <v>857</v>
@@ -10113,7 +10113,7 @@
         <v>856</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T114" s="2" t="s">
         <v>857</v>
@@ -10175,7 +10175,7 @@
         <v>856</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T115" s="2" t="s">
         <v>857</v>
@@ -10237,7 +10237,7 @@
         <v>856</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T116" s="2" t="s">
         <v>857</v>
@@ -10299,7 +10299,7 @@
         <v>856</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T117" s="2" t="s">
         <v>857</v>
@@ -10361,7 +10361,7 @@
         <v>856</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T118" s="2" t="s">
         <v>857</v>
@@ -10423,7 +10423,7 @@
         <v>856</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T119" s="2" t="s">
         <v>857</v>
@@ -10485,7 +10485,7 @@
         <v>856</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T120" s="2" t="s">
         <v>857</v>
@@ -10547,7 +10547,7 @@
         <v>856</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T121" s="2" t="s">
         <v>857</v>
@@ -10609,7 +10609,7 @@
         <v>856</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T122" s="2" t="s">
         <v>857</v>
@@ -10671,7 +10671,7 @@
         <v>856</v>
       </c>
       <c r="S123" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T123" s="2" t="s">
         <v>857</v>
@@ -10733,7 +10733,7 @@
         <v>856</v>
       </c>
       <c r="S124" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T124" s="2" t="s">
         <v>857</v>
@@ -10795,7 +10795,7 @@
         <v>856</v>
       </c>
       <c r="S125" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T125" s="2" t="s">
         <v>857</v>
@@ -10857,7 +10857,7 @@
         <v>856</v>
       </c>
       <c r="S126" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T126" s="2" t="s">
         <v>857</v>
@@ -10919,7 +10919,7 @@
         <v>856</v>
       </c>
       <c r="S127" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T127" s="2" t="s">
         <v>857</v>
@@ -10981,7 +10981,7 @@
         <v>856</v>
       </c>
       <c r="S128" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T128" s="2" t="s">
         <v>857</v>
@@ -11043,7 +11043,7 @@
         <v>856</v>
       </c>
       <c r="S129" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T129" s="2" t="s">
         <v>857</v>
@@ -11105,7 +11105,7 @@
         <v>856</v>
       </c>
       <c r="S130" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T130" s="2" t="s">
         <v>857</v>
@@ -11167,7 +11167,7 @@
         <v>856</v>
       </c>
       <c r="S131" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T131" s="2" t="s">
         <v>857</v>
@@ -11229,7 +11229,7 @@
         <v>856</v>
       </c>
       <c r="S132" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T132" s="2" t="s">
         <v>857</v>
@@ -11291,7 +11291,7 @@
         <v>856</v>
       </c>
       <c r="S133" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T133" s="2" t="s">
         <v>857</v>
@@ -11353,7 +11353,7 @@
         <v>856</v>
       </c>
       <c r="S134" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T134" s="2" t="s">
         <v>857</v>
@@ -11415,7 +11415,7 @@
         <v>856</v>
       </c>
       <c r="S135" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T135" s="2" t="s">
         <v>857</v>
@@ -11477,7 +11477,7 @@
         <v>856</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T136" s="2" t="s">
         <v>857</v>
@@ -11539,7 +11539,7 @@
         <v>856</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T137" s="2" t="s">
         <v>857</v>
@@ -11601,7 +11601,7 @@
         <v>856</v>
       </c>
       <c r="S138" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T138" s="2" t="s">
         <v>857</v>
@@ -11663,7 +11663,7 @@
         <v>856</v>
       </c>
       <c r="S139" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T139" s="2" t="s">
         <v>857</v>
@@ -11725,7 +11725,7 @@
         <v>856</v>
       </c>
       <c r="S140" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T140" s="2" t="s">
         <v>857</v>
@@ -11787,7 +11787,7 @@
         <v>856</v>
       </c>
       <c r="S141" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T141" s="2" t="s">
         <v>857</v>
@@ -11849,7 +11849,7 @@
         <v>856</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T142" s="2" t="s">
         <v>857</v>
@@ -11911,7 +11911,7 @@
         <v>856</v>
       </c>
       <c r="S143" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T143" s="2" t="s">
         <v>857</v>
@@ -11973,7 +11973,7 @@
         <v>856</v>
       </c>
       <c r="S144" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T144" s="2" t="s">
         <v>857</v>
@@ -12035,7 +12035,7 @@
         <v>856</v>
       </c>
       <c r="S145" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T145" s="2" t="s">
         <v>857</v>
@@ -12097,7 +12097,7 @@
         <v>856</v>
       </c>
       <c r="S146" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T146" s="2" t="s">
         <v>857</v>
@@ -12159,7 +12159,7 @@
         <v>856</v>
       </c>
       <c r="S147" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T147" s="2" t="s">
         <v>857</v>
@@ -12221,7 +12221,7 @@
         <v>856</v>
       </c>
       <c r="S148" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T148" s="2" t="s">
         <v>857</v>
@@ -12283,7 +12283,7 @@
         <v>856</v>
       </c>
       <c r="S149" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T149" s="2" t="s">
         <v>857</v>
@@ -12345,7 +12345,7 @@
         <v>856</v>
       </c>
       <c r="S150" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T150" s="2" t="s">
         <v>857</v>
@@ -12407,7 +12407,7 @@
         <v>856</v>
       </c>
       <c r="S151" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T151" s="2" t="s">
         <v>857</v>
@@ -12469,7 +12469,7 @@
         <v>856</v>
       </c>
       <c r="S152" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T152" s="2" t="s">
         <v>857</v>
@@ -12531,7 +12531,7 @@
         <v>856</v>
       </c>
       <c r="S153" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T153" s="2" t="s">
         <v>857</v>
@@ -12593,7 +12593,7 @@
         <v>856</v>
       </c>
       <c r="S154" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T154" s="2" t="s">
         <v>857</v>
@@ -12655,7 +12655,7 @@
         <v>856</v>
       </c>
       <c r="S155" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T155" s="2" t="s">
         <v>857</v>
@@ -12717,7 +12717,7 @@
         <v>856</v>
       </c>
       <c r="S156" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T156" s="2" t="s">
         <v>857</v>
@@ -12779,7 +12779,7 @@
         <v>856</v>
       </c>
       <c r="S157" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T157" s="2" t="s">
         <v>857</v>
@@ -12841,7 +12841,7 @@
         <v>856</v>
       </c>
       <c r="S158" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T158" s="2" t="s">
         <v>857</v>
@@ -12903,7 +12903,7 @@
         <v>856</v>
       </c>
       <c r="S159" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T159" s="2" t="s">
         <v>857</v>
@@ -12965,7 +12965,7 @@
         <v>856</v>
       </c>
       <c r="S160" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T160" s="2" t="s">
         <v>857</v>
@@ -13027,7 +13027,7 @@
         <v>856</v>
       </c>
       <c r="S161" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T161" s="2" t="s">
         <v>857</v>
@@ -13089,7 +13089,7 @@
         <v>856</v>
       </c>
       <c r="S162" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T162" s="2" t="s">
         <v>857</v>
@@ -13151,7 +13151,7 @@
         <v>856</v>
       </c>
       <c r="S163" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T163" s="2" t="s">
         <v>857</v>
@@ -13213,7 +13213,7 @@
         <v>856</v>
       </c>
       <c r="S164" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T164" s="2" t="s">
         <v>857</v>
@@ -13275,7 +13275,7 @@
         <v>856</v>
       </c>
       <c r="S165" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T165" s="2" t="s">
         <v>857</v>
@@ -13337,7 +13337,7 @@
         <v>856</v>
       </c>
       <c r="S166" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T166" s="2" t="s">
         <v>857</v>
@@ -13399,7 +13399,7 @@
         <v>856</v>
       </c>
       <c r="S167" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T167" s="2" t="s">
         <v>857</v>
@@ -13461,7 +13461,7 @@
         <v>856</v>
       </c>
       <c r="S168" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T168" s="2" t="s">
         <v>857</v>
@@ -13523,7 +13523,7 @@
         <v>856</v>
       </c>
       <c r="S169" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T169" s="2" t="s">
         <v>857</v>
@@ -13585,7 +13585,7 @@
         <v>856</v>
       </c>
       <c r="S170" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T170" s="2" t="s">
         <v>857</v>
@@ -13647,7 +13647,7 @@
         <v>856</v>
       </c>
       <c r="S171" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T171" s="2" t="s">
         <v>857</v>
@@ -13709,7 +13709,7 @@
         <v>856</v>
       </c>
       <c r="S172" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T172" s="2" t="s">
         <v>857</v>
@@ -13771,7 +13771,7 @@
         <v>856</v>
       </c>
       <c r="S173" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T173" s="2" t="s">
         <v>857</v>
@@ -13833,7 +13833,7 @@
         <v>856</v>
       </c>
       <c r="S174" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T174" s="2" t="s">
         <v>857</v>
@@ -13895,7 +13895,7 @@
         <v>856</v>
       </c>
       <c r="S175" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T175" s="2" t="s">
         <v>857</v>
@@ -13957,7 +13957,7 @@
         <v>856</v>
       </c>
       <c r="S176" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T176" s="2" t="s">
         <v>857</v>
@@ -14019,7 +14019,7 @@
         <v>856</v>
       </c>
       <c r="S177" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T177" s="2" t="s">
         <v>857</v>
@@ -14081,7 +14081,7 @@
         <v>856</v>
       </c>
       <c r="S178" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T178" s="2" t="s">
         <v>857</v>
@@ -14143,7 +14143,7 @@
         <v>856</v>
       </c>
       <c r="S179" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T179" s="2" t="s">
         <v>857</v>
@@ -14205,7 +14205,7 @@
         <v>856</v>
       </c>
       <c r="S180" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T180" s="2" t="s">
         <v>857</v>
@@ -14267,7 +14267,7 @@
         <v>856</v>
       </c>
       <c r="S181" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T181" s="2" t="s">
         <v>857</v>
@@ -14329,7 +14329,7 @@
         <v>856</v>
       </c>
       <c r="S182" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T182" s="2" t="s">
         <v>857</v>
@@ -14391,7 +14391,7 @@
         <v>856</v>
       </c>
       <c r="S183" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T183" s="2" t="s">
         <v>857</v>
@@ -14453,7 +14453,7 @@
         <v>856</v>
       </c>
       <c r="S184" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T184" s="2" t="s">
         <v>857</v>
@@ -14515,7 +14515,7 @@
         <v>856</v>
       </c>
       <c r="S185" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T185" s="2" t="s">
         <v>857</v>
@@ -14577,7 +14577,7 @@
         <v>856</v>
       </c>
       <c r="S186" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T186" s="2" t="s">
         <v>857</v>
@@ -14639,7 +14639,7 @@
         <v>856</v>
       </c>
       <c r="S187" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T187" s="2" t="s">
         <v>857</v>
@@ -14701,7 +14701,7 @@
         <v>856</v>
       </c>
       <c r="S188" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T188" s="2" t="s">
         <v>857</v>
@@ -14763,7 +14763,7 @@
         <v>856</v>
       </c>
       <c r="S189" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T189" s="2" t="s">
         <v>857</v>
@@ -14825,7 +14825,7 @@
         <v>856</v>
       </c>
       <c r="S190" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T190" s="2" t="s">
         <v>857</v>
@@ -14887,7 +14887,7 @@
         <v>856</v>
       </c>
       <c r="S191" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T191" s="2" t="s">
         <v>857</v>
@@ -14949,7 +14949,7 @@
         <v>856</v>
       </c>
       <c r="S192" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T192" s="2" t="s">
         <v>857</v>
@@ -15011,7 +15011,7 @@
         <v>856</v>
       </c>
       <c r="S193" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T193" s="2" t="s">
         <v>857</v>
@@ -15073,7 +15073,7 @@
         <v>856</v>
       </c>
       <c r="S194" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T194" s="2" t="s">
         <v>857</v>
@@ -15135,7 +15135,7 @@
         <v>856</v>
       </c>
       <c r="S195" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T195" s="2" t="s">
         <v>857</v>
@@ -15197,7 +15197,7 @@
         <v>856</v>
       </c>
       <c r="S196" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T196" s="2" t="s">
         <v>857</v>
@@ -15259,7 +15259,7 @@
         <v>856</v>
       </c>
       <c r="S197" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T197" s="2" t="s">
         <v>857</v>
@@ -15321,7 +15321,7 @@
         <v>856</v>
       </c>
       <c r="S198" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T198" s="2" t="s">
         <v>857</v>
@@ -15383,7 +15383,7 @@
         <v>856</v>
       </c>
       <c r="S199" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T199" s="2" t="s">
         <v>857</v>
@@ -15445,7 +15445,7 @@
         <v>856</v>
       </c>
       <c r="S200" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T200" s="2" t="s">
         <v>857</v>
@@ -15507,7 +15507,7 @@
         <v>856</v>
       </c>
       <c r="S201" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T201" s="2" t="s">
         <v>857</v>
@@ -15569,7 +15569,7 @@
         <v>856</v>
       </c>
       <c r="S202" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T202" s="2" t="s">
         <v>857</v>
@@ -15631,7 +15631,7 @@
         <v>856</v>
       </c>
       <c r="S203" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T203" s="2" t="s">
         <v>857</v>
@@ -15693,7 +15693,7 @@
         <v>856</v>
       </c>
       <c r="S204" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T204" s="2" t="s">
         <v>857</v>
@@ -15755,7 +15755,7 @@
         <v>856</v>
       </c>
       <c r="S205" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T205" s="2" t="s">
         <v>857</v>
@@ -15817,7 +15817,7 @@
         <v>856</v>
       </c>
       <c r="S206" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T206" s="2" t="s">
         <v>857</v>
@@ -15879,7 +15879,7 @@
         <v>856</v>
       </c>
       <c r="S207" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T207" s="2" t="s">
         <v>857</v>
@@ -15941,7 +15941,7 @@
         <v>856</v>
       </c>
       <c r="S208" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T208" s="2" t="s">
         <v>857</v>
@@ -16003,7 +16003,7 @@
         <v>856</v>
       </c>
       <c r="S209" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T209" s="2" t="s">
         <v>857</v>
@@ -16065,7 +16065,7 @@
         <v>856</v>
       </c>
       <c r="S210" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T210" s="2" t="s">
         <v>857</v>
@@ -16127,7 +16127,7 @@
         <v>856</v>
       </c>
       <c r="S211" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T211" s="2" t="s">
         <v>857</v>
@@ -16189,7 +16189,7 @@
         <v>856</v>
       </c>
       <c r="S212" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T212" s="2" t="s">
         <v>857</v>
@@ -16251,7 +16251,7 @@
         <v>856</v>
       </c>
       <c r="S213" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T213" s="2" t="s">
         <v>857</v>
@@ -16313,7 +16313,7 @@
         <v>856</v>
       </c>
       <c r="S214" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T214" s="2" t="s">
         <v>857</v>
@@ -16375,7 +16375,7 @@
         <v>856</v>
       </c>
       <c r="S215" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T215" s="2" t="s">
         <v>857</v>
@@ -16437,7 +16437,7 @@
         <v>856</v>
       </c>
       <c r="S216" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T216" s="2" t="s">
         <v>857</v>
@@ -16499,7 +16499,7 @@
         <v>856</v>
       </c>
       <c r="S217" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T217" s="2" t="s">
         <v>857</v>
@@ -16561,7 +16561,7 @@
         <v>856</v>
       </c>
       <c r="S218" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T218" s="2" t="s">
         <v>857</v>
@@ -16623,7 +16623,7 @@
         <v>856</v>
       </c>
       <c r="S219" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T219" s="2" t="s">
         <v>857</v>
@@ -16685,7 +16685,7 @@
         <v>856</v>
       </c>
       <c r="S220" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T220" s="2" t="s">
         <v>857</v>
@@ -16747,7 +16747,7 @@
         <v>856</v>
       </c>
       <c r="S221" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T221" s="2" t="s">
         <v>857</v>
@@ -16809,7 +16809,7 @@
         <v>856</v>
       </c>
       <c r="S222" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T222" s="2" t="s">
         <v>857</v>
@@ -16871,7 +16871,7 @@
         <v>856</v>
       </c>
       <c r="S223" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T223" s="2" t="s">
         <v>857</v>
@@ -16933,7 +16933,7 @@
         <v>856</v>
       </c>
       <c r="S224" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T224" s="2" t="s">
         <v>857</v>
@@ -16995,7 +16995,7 @@
         <v>856</v>
       </c>
       <c r="S225" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T225" s="2" t="s">
         <v>857</v>
@@ -17057,7 +17057,7 @@
         <v>856</v>
       </c>
       <c r="S226" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T226" s="2" t="s">
         <v>857</v>
@@ -17119,7 +17119,7 @@
         <v>856</v>
       </c>
       <c r="S227" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T227" s="2" t="s">
         <v>857</v>
@@ -17181,7 +17181,7 @@
         <v>856</v>
       </c>
       <c r="S228" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T228" s="2" t="s">
         <v>857</v>
@@ -17243,7 +17243,7 @@
         <v>856</v>
       </c>
       <c r="S229" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T229" s="2" t="s">
         <v>857</v>
@@ -17305,7 +17305,7 @@
         <v>856</v>
       </c>
       <c r="S230" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T230" s="2" t="s">
         <v>857</v>
@@ -17367,7 +17367,7 @@
         <v>856</v>
       </c>
       <c r="S231" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T231" s="2" t="s">
         <v>857</v>
@@ -17429,7 +17429,7 @@
         <v>856</v>
       </c>
       <c r="S232" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T232" s="2" t="s">
         <v>857</v>
@@ -17491,7 +17491,7 @@
         <v>856</v>
       </c>
       <c r="S233" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T233" s="2" t="s">
         <v>857</v>
@@ -17553,7 +17553,7 @@
         <v>856</v>
       </c>
       <c r="S234" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T234" s="2" t="s">
         <v>857</v>
@@ -17615,7 +17615,7 @@
         <v>856</v>
       </c>
       <c r="S235" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T235" s="2" t="s">
         <v>857</v>
@@ -17677,7 +17677,7 @@
         <v>856</v>
       </c>
       <c r="S236" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T236" s="2" t="s">
         <v>857</v>
@@ -17739,7 +17739,7 @@
         <v>856</v>
       </c>
       <c r="S237" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T237" s="2" t="s">
         <v>857</v>
@@ -17801,7 +17801,7 @@
         <v>856</v>
       </c>
       <c r="S238" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T238" s="2" t="s">
         <v>857</v>
@@ -17863,7 +17863,7 @@
         <v>856</v>
       </c>
       <c r="S239" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T239" s="2" t="s">
         <v>857</v>
@@ -17925,7 +17925,7 @@
         <v>856</v>
       </c>
       <c r="S240" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T240" s="2" t="s">
         <v>857</v>
@@ -17987,7 +17987,7 @@
         <v>856</v>
       </c>
       <c r="S241" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T241" s="2" t="s">
         <v>857</v>
@@ -18049,7 +18049,7 @@
         <v>856</v>
       </c>
       <c r="S242" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T242" s="2" t="s">
         <v>857</v>
@@ -18111,7 +18111,7 @@
         <v>856</v>
       </c>
       <c r="S243" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T243" s="2" t="s">
         <v>857</v>
@@ -18173,7 +18173,7 @@
         <v>856</v>
       </c>
       <c r="S244" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T244" s="2" t="s">
         <v>857</v>
@@ -18235,7 +18235,7 @@
         <v>856</v>
       </c>
       <c r="S245" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T245" s="2" t="s">
         <v>857</v>
@@ -18297,7 +18297,7 @@
         <v>856</v>
       </c>
       <c r="S246" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T246" s="2" t="s">
         <v>857</v>
@@ -18359,7 +18359,7 @@
         <v>856</v>
       </c>
       <c r="S247" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T247" s="2" t="s">
         <v>857</v>
@@ -18421,7 +18421,7 @@
         <v>856</v>
       </c>
       <c r="S248" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T248" s="2" t="s">
         <v>857</v>
@@ -18483,7 +18483,7 @@
         <v>856</v>
       </c>
       <c r="S249" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T249" s="2" t="s">
         <v>857</v>
@@ -18545,7 +18545,7 @@
         <v>856</v>
       </c>
       <c r="S250" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T250" s="2" t="s">
         <v>857</v>
@@ -18607,7 +18607,7 @@
         <v>856</v>
       </c>
       <c r="S251" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T251" s="2" t="s">
         <v>857</v>
@@ -18669,7 +18669,7 @@
         <v>856</v>
       </c>
       <c r="S252" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T252" s="2" t="s">
         <v>857</v>
@@ -18731,7 +18731,7 @@
         <v>856</v>
       </c>
       <c r="S253" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T253" s="2" t="s">
         <v>857</v>
@@ -18793,7 +18793,7 @@
         <v>856</v>
       </c>
       <c r="S254" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T254" s="2" t="s">
         <v>857</v>
@@ -18855,7 +18855,7 @@
         <v>856</v>
       </c>
       <c r="S255" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T255" s="2" t="s">
         <v>857</v>
@@ -18917,7 +18917,7 @@
         <v>856</v>
       </c>
       <c r="S256" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T256" s="2" t="s">
         <v>857</v>
@@ -18979,7 +18979,7 @@
         <v>856</v>
       </c>
       <c r="S257" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T257" s="2" t="s">
         <v>857</v>
@@ -19041,7 +19041,7 @@
         <v>856</v>
       </c>
       <c r="S258" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T258" s="2" t="s">
         <v>857</v>
@@ -19103,7 +19103,7 @@
         <v>856</v>
       </c>
       <c r="S259" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T259" s="2" t="s">
         <v>857</v>
@@ -19165,7 +19165,7 @@
         <v>856</v>
       </c>
       <c r="S260" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T260" s="2" t="s">
         <v>857</v>
@@ -19227,7 +19227,7 @@
         <v>856</v>
       </c>
       <c r="S261" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T261" s="2" t="s">
         <v>857</v>
@@ -19289,7 +19289,7 @@
         <v>856</v>
       </c>
       <c r="S262" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T262" s="2" t="s">
         <v>857</v>
@@ -19351,7 +19351,7 @@
         <v>856</v>
       </c>
       <c r="S263" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T263" s="2" t="s">
         <v>857</v>
@@ -19413,7 +19413,7 @@
         <v>856</v>
       </c>
       <c r="S264" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T264" s="2" t="s">
         <v>857</v>
@@ -19475,7 +19475,7 @@
         <v>856</v>
       </c>
       <c r="S265" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T265" s="2" t="s">
         <v>857</v>
@@ -19537,7 +19537,7 @@
         <v>856</v>
       </c>
       <c r="S266" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T266" s="2" t="s">
         <v>857</v>
@@ -19599,7 +19599,7 @@
         <v>856</v>
       </c>
       <c r="S267" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T267" s="2" t="s">
         <v>857</v>
@@ -19661,7 +19661,7 @@
         <v>856</v>
       </c>
       <c r="S268" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T268" s="2" t="s">
         <v>857</v>
@@ -19723,7 +19723,7 @@
         <v>856</v>
       </c>
       <c r="S269" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T269" s="2" t="s">
         <v>857</v>
@@ -19785,7 +19785,7 @@
         <v>856</v>
       </c>
       <c r="S270" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T270" s="2" t="s">
         <v>857</v>
@@ -19847,7 +19847,7 @@
         <v>856</v>
       </c>
       <c r="S271" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T271" s="2" t="s">
         <v>857</v>
@@ -19909,7 +19909,7 @@
         <v>856</v>
       </c>
       <c r="S272" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T272" s="2" t="s">
         <v>857</v>
@@ -19971,7 +19971,7 @@
         <v>856</v>
       </c>
       <c r="S273" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T273" s="2" t="s">
         <v>857</v>
@@ -20033,7 +20033,7 @@
         <v>856</v>
       </c>
       <c r="S274" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T274" s="2" t="s">
         <v>857</v>
@@ -20095,7 +20095,7 @@
         <v>856</v>
       </c>
       <c r="S275" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T275" s="2" t="s">
         <v>857</v>
@@ -20157,7 +20157,7 @@
         <v>856</v>
       </c>
       <c r="S276" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T276" s="2" t="s">
         <v>857</v>
@@ -20219,7 +20219,7 @@
         <v>856</v>
       </c>
       <c r="S277" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T277" s="2" t="s">
         <v>857</v>
@@ -20281,7 +20281,7 @@
         <v>856</v>
       </c>
       <c r="S278" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T278" s="2" t="s">
         <v>857</v>
@@ -20343,7 +20343,7 @@
         <v>856</v>
       </c>
       <c r="S279" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T279" s="2" t="s">
         <v>857</v>
@@ -20405,7 +20405,7 @@
         <v>856</v>
       </c>
       <c r="S280" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T280" s="2" t="s">
         <v>857</v>
@@ -20467,7 +20467,7 @@
         <v>856</v>
       </c>
       <c r="S281" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T281" s="2" t="s">
         <v>857</v>
@@ -20529,7 +20529,7 @@
         <v>856</v>
       </c>
       <c r="S282" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T282" s="2" t="s">
         <v>857</v>
@@ -20591,7 +20591,7 @@
         <v>856</v>
       </c>
       <c r="S283" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T283" s="2" t="s">
         <v>857</v>
@@ -20653,7 +20653,7 @@
         <v>856</v>
       </c>
       <c r="S284" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T284" s="2" t="s">
         <v>857</v>
@@ -20715,7 +20715,7 @@
         <v>856</v>
       </c>
       <c r="S285" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T285" s="2" t="s">
         <v>857</v>
@@ -20777,7 +20777,7 @@
         <v>856</v>
       </c>
       <c r="S286" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T286" s="2" t="s">
         <v>857</v>
@@ -20839,7 +20839,7 @@
         <v>856</v>
       </c>
       <c r="S287" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T287" s="2" t="s">
         <v>857</v>
@@ -20901,7 +20901,7 @@
         <v>856</v>
       </c>
       <c r="S288" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T288" s="2" t="s">
         <v>857</v>
@@ -20963,7 +20963,7 @@
         <v>856</v>
       </c>
       <c r="S289" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T289" s="2" t="s">
         <v>857</v>
@@ -21025,7 +21025,7 @@
         <v>856</v>
       </c>
       <c r="S290" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T290" s="2" t="s">
         <v>857</v>
@@ -21087,7 +21087,7 @@
         <v>856</v>
       </c>
       <c r="S291" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T291" s="2" t="s">
         <v>857</v>
@@ -21149,7 +21149,7 @@
         <v>856</v>
       </c>
       <c r="S292" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T292" s="2" t="s">
         <v>857</v>
@@ -21211,7 +21211,7 @@
         <v>856</v>
       </c>
       <c r="S293" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T293" s="2" t="s">
         <v>857</v>
@@ -21273,7 +21273,7 @@
         <v>856</v>
       </c>
       <c r="S294" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T294" s="2" t="s">
         <v>857</v>
@@ -21335,7 +21335,7 @@
         <v>856</v>
       </c>
       <c r="S295" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T295" s="2" t="s">
         <v>857</v>
@@ -21397,7 +21397,7 @@
         <v>856</v>
       </c>
       <c r="S296" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T296" s="2" t="s">
         <v>857</v>
@@ -21459,7 +21459,7 @@
         <v>856</v>
       </c>
       <c r="S297" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T297" s="2" t="s">
         <v>857</v>
@@ -21521,7 +21521,7 @@
         <v>856</v>
       </c>
       <c r="S298" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T298" s="2" t="s">
         <v>857</v>
@@ -21583,7 +21583,7 @@
         <v>856</v>
       </c>
       <c r="S299" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T299" s="2" t="s">
         <v>857</v>
@@ -21645,7 +21645,7 @@
         <v>856</v>
       </c>
       <c r="S300" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T300" s="2" t="s">
         <v>857</v>
@@ -21707,7 +21707,7 @@
         <v>856</v>
       </c>
       <c r="S301" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T301" s="2" t="s">
         <v>857</v>
@@ -21769,7 +21769,7 @@
         <v>856</v>
       </c>
       <c r="S302" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T302" s="2" t="s">
         <v>857</v>
@@ -21831,7 +21831,7 @@
         <v>856</v>
       </c>
       <c r="S303" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T303" s="2" t="s">
         <v>857</v>
@@ -21893,7 +21893,7 @@
         <v>856</v>
       </c>
       <c r="S304" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T304" s="2" t="s">
         <v>857</v>
@@ -21955,7 +21955,7 @@
         <v>856</v>
       </c>
       <c r="S305" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T305" s="2" t="s">
         <v>857</v>
@@ -22017,7 +22017,7 @@
         <v>856</v>
       </c>
       <c r="S306" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T306" s="2" t="s">
         <v>857</v>
@@ -22079,7 +22079,7 @@
         <v>856</v>
       </c>
       <c r="S307" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T307" s="2" t="s">
         <v>857</v>
@@ -22141,7 +22141,7 @@
         <v>856</v>
       </c>
       <c r="S308" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T308" s="2" t="s">
         <v>857</v>
@@ -22203,7 +22203,7 @@
         <v>856</v>
       </c>
       <c r="S309" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T309" s="2" t="s">
         <v>857</v>
@@ -22265,7 +22265,7 @@
         <v>856</v>
       </c>
       <c r="S310" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T310" s="2" t="s">
         <v>857</v>
@@ -22327,7 +22327,7 @@
         <v>856</v>
       </c>
       <c r="S311" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T311" s="2" t="s">
         <v>857</v>
@@ -22389,7 +22389,7 @@
         <v>856</v>
       </c>
       <c r="S312" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T312" s="2" t="s">
         <v>857</v>
@@ -22451,7 +22451,7 @@
         <v>856</v>
       </c>
       <c r="S313" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T313" s="2" t="s">
         <v>857</v>
@@ -22513,7 +22513,7 @@
         <v>856</v>
       </c>
       <c r="S314" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T314" s="2" t="s">
         <v>857</v>
@@ -22575,7 +22575,7 @@
         <v>856</v>
       </c>
       <c r="S315" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T315" s="2" t="s">
         <v>857</v>
@@ -22637,7 +22637,7 @@
         <v>856</v>
       </c>
       <c r="S316" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T316" s="2" t="s">
         <v>857</v>
@@ -22699,7 +22699,7 @@
         <v>856</v>
       </c>
       <c r="S317" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T317" s="2" t="s">
         <v>857</v>
@@ -22761,7 +22761,7 @@
         <v>856</v>
       </c>
       <c r="S318" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T318" s="2" t="s">
         <v>857</v>
@@ -22823,7 +22823,7 @@
         <v>856</v>
       </c>
       <c r="S319" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T319" s="2" t="s">
         <v>857</v>
@@ -22885,7 +22885,7 @@
         <v>856</v>
       </c>
       <c r="S320" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T320" s="2" t="s">
         <v>857</v>
@@ -22947,7 +22947,7 @@
         <v>856</v>
       </c>
       <c r="S321" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T321" s="2" t="s">
         <v>857</v>
@@ -23009,7 +23009,7 @@
         <v>856</v>
       </c>
       <c r="S322" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T322" s="2" t="s">
         <v>857</v>
@@ -23071,7 +23071,7 @@
         <v>856</v>
       </c>
       <c r="S323" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T323" s="2" t="s">
         <v>857</v>
@@ -23133,7 +23133,7 @@
         <v>856</v>
       </c>
       <c r="S324" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T324" s="2" t="s">
         <v>857</v>
@@ -23195,7 +23195,7 @@
         <v>856</v>
       </c>
       <c r="S325" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T325" s="2" t="s">
         <v>857</v>
@@ -23257,7 +23257,7 @@
         <v>856</v>
       </c>
       <c r="S326" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T326" s="2" t="s">
         <v>857</v>
@@ -23319,7 +23319,7 @@
         <v>856</v>
       </c>
       <c r="S327" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T327" s="2" t="s">
         <v>857</v>
@@ -23381,7 +23381,7 @@
         <v>856</v>
       </c>
       <c r="S328" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T328" s="2" t="s">
         <v>857</v>
@@ -23443,7 +23443,7 @@
         <v>856</v>
       </c>
       <c r="S329" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T329" s="2" t="s">
         <v>857</v>
@@ -23505,7 +23505,7 @@
         <v>856</v>
       </c>
       <c r="S330" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T330" s="2" t="s">
         <v>857</v>
@@ -23567,7 +23567,7 @@
         <v>856</v>
       </c>
       <c r="S331" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T331" s="2" t="s">
         <v>857</v>
@@ -23629,7 +23629,7 @@
         <v>856</v>
       </c>
       <c r="S332" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T332" s="2" t="s">
         <v>857</v>
@@ -23691,7 +23691,7 @@
         <v>856</v>
       </c>
       <c r="S333" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T333" s="2" t="s">
         <v>857</v>
@@ -23753,7 +23753,7 @@
         <v>856</v>
       </c>
       <c r="S334" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T334" s="2" t="s">
         <v>857</v>
@@ -23815,7 +23815,7 @@
         <v>856</v>
       </c>
       <c r="S335" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T335" s="2" t="s">
         <v>857</v>
@@ -23877,7 +23877,7 @@
         <v>856</v>
       </c>
       <c r="S336" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T336" s="2" t="s">
         <v>857</v>
@@ -23939,7 +23939,7 @@
         <v>856</v>
       </c>
       <c r="S337" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T337" s="2" t="s">
         <v>857</v>
@@ -24001,7 +24001,7 @@
         <v>856</v>
       </c>
       <c r="S338" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T338" s="2" t="s">
         <v>857</v>
@@ -24063,7 +24063,7 @@
         <v>856</v>
       </c>
       <c r="S339" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T339" s="2" t="s">
         <v>857</v>
@@ -24125,7 +24125,7 @@
         <v>856</v>
       </c>
       <c r="S340" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T340" s="2" t="s">
         <v>857</v>
@@ -24187,7 +24187,7 @@
         <v>856</v>
       </c>
       <c r="S341" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T341" s="2" t="s">
         <v>857</v>
@@ -24249,7 +24249,7 @@
         <v>856</v>
       </c>
       <c r="S342" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T342" s="2" t="s">
         <v>857</v>
@@ -24311,7 +24311,7 @@
         <v>856</v>
       </c>
       <c r="S343" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T343" s="2" t="s">
         <v>857</v>
@@ -24373,7 +24373,7 @@
         <v>856</v>
       </c>
       <c r="S344" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T344" s="2" t="s">
         <v>857</v>
@@ -24435,7 +24435,7 @@
         <v>856</v>
       </c>
       <c r="S345" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T345" s="2" t="s">
         <v>857</v>
@@ -24497,7 +24497,7 @@
         <v>856</v>
       </c>
       <c r="S346" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T346" s="2" t="s">
         <v>857</v>
@@ -24559,7 +24559,7 @@
         <v>856</v>
       </c>
       <c r="S347" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T347" s="2" t="s">
         <v>857</v>
@@ -24621,7 +24621,7 @@
         <v>856</v>
       </c>
       <c r="S348" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T348" s="2" t="s">
         <v>857</v>
@@ -24683,7 +24683,7 @@
         <v>856</v>
       </c>
       <c r="S349" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T349" s="2" t="s">
         <v>857</v>
@@ -24745,7 +24745,7 @@
         <v>856</v>
       </c>
       <c r="S350" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T350" s="2" t="s">
         <v>857</v>
@@ -24807,7 +24807,7 @@
         <v>856</v>
       </c>
       <c r="S351" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T351" s="2" t="s">
         <v>857</v>
@@ -24869,7 +24869,7 @@
         <v>856</v>
       </c>
       <c r="S352" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T352" s="2" t="s">
         <v>857</v>
@@ -24931,7 +24931,7 @@
         <v>856</v>
       </c>
       <c r="S353" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T353" s="2" t="s">
         <v>857</v>
@@ -24993,7 +24993,7 @@
         <v>856</v>
       </c>
       <c r="S354" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T354" s="2" t="s">
         <v>857</v>
@@ -25055,7 +25055,7 @@
         <v>856</v>
       </c>
       <c r="S355" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T355" s="2" t="s">
         <v>857</v>
@@ -25117,7 +25117,7 @@
         <v>856</v>
       </c>
       <c r="S356" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T356" s="2" t="s">
         <v>857</v>
@@ -25179,7 +25179,7 @@
         <v>856</v>
       </c>
       <c r="S357" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T357" s="2" t="s">
         <v>857</v>
@@ -25241,7 +25241,7 @@
         <v>856</v>
       </c>
       <c r="S358" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T358" s="2" t="s">
         <v>857</v>
@@ -25303,7 +25303,7 @@
         <v>856</v>
       </c>
       <c r="S359" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T359" s="2" t="s">
         <v>857</v>
@@ -25365,7 +25365,7 @@
         <v>856</v>
       </c>
       <c r="S360" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T360" s="2" t="s">
         <v>857</v>
@@ -25427,7 +25427,7 @@
         <v>856</v>
       </c>
       <c r="S361" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T361" s="2" t="s">
         <v>857</v>
@@ -25489,7 +25489,7 @@
         <v>856</v>
       </c>
       <c r="S362" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T362" s="2" t="s">
         <v>857</v>
@@ -25551,7 +25551,7 @@
         <v>856</v>
       </c>
       <c r="S363" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T363" s="2" t="s">
         <v>857</v>
@@ -25613,7 +25613,7 @@
         <v>856</v>
       </c>
       <c r="S364" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T364" s="2" t="s">
         <v>857</v>
@@ -25675,7 +25675,7 @@
         <v>856</v>
       </c>
       <c r="S365" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T365" s="2" t="s">
         <v>857</v>
@@ -25737,7 +25737,7 @@
         <v>856</v>
       </c>
       <c r="S366" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T366" s="2" t="s">
         <v>857</v>
@@ -25799,7 +25799,7 @@
         <v>856</v>
       </c>
       <c r="S367" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T367" s="2" t="s">
         <v>857</v>
@@ -25861,7 +25861,7 @@
         <v>856</v>
       </c>
       <c r="S368" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T368" s="2" t="s">
         <v>857</v>
@@ -25923,7 +25923,7 @@
         <v>856</v>
       </c>
       <c r="S369" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T369" s="2" t="s">
         <v>857</v>
@@ -25985,7 +25985,7 @@
         <v>856</v>
       </c>
       <c r="S370" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T370" s="2" t="s">
         <v>857</v>
@@ -26047,7 +26047,7 @@
         <v>856</v>
       </c>
       <c r="S371" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T371" s="2" t="s">
         <v>857</v>
@@ -26109,7 +26109,7 @@
         <v>856</v>
       </c>
       <c r="S372" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T372" s="2" t="s">
         <v>857</v>
@@ -26171,7 +26171,7 @@
         <v>856</v>
       </c>
       <c r="S373" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T373" s="2" t="s">
         <v>857</v>
@@ -26233,7 +26233,7 @@
         <v>856</v>
       </c>
       <c r="S374" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T374" s="2" t="s">
         <v>857</v>
@@ -26295,7 +26295,7 @@
         <v>856</v>
       </c>
       <c r="S375" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T375" s="2" t="s">
         <v>857</v>
@@ -26357,7 +26357,7 @@
         <v>856</v>
       </c>
       <c r="S376" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T376" s="2" t="s">
         <v>857</v>
@@ -26419,7 +26419,7 @@
         <v>856</v>
       </c>
       <c r="S377" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T377" s="2" t="s">
         <v>857</v>
@@ -26481,7 +26481,7 @@
         <v>856</v>
       </c>
       <c r="S378" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T378" s="2" t="s">
         <v>857</v>
@@ -26543,7 +26543,7 @@
         <v>856</v>
       </c>
       <c r="S379" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T379" s="2" t="s">
         <v>857</v>
@@ -26605,7 +26605,7 @@
         <v>856</v>
       </c>
       <c r="S380" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T380" s="2" t="s">
         <v>857</v>
@@ -26667,7 +26667,7 @@
         <v>856</v>
       </c>
       <c r="S381" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T381" s="2" t="s">
         <v>857</v>
@@ -26729,7 +26729,7 @@
         <v>856</v>
       </c>
       <c r="S382" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T382" s="2" t="s">
         <v>857</v>
@@ -26791,7 +26791,7 @@
         <v>856</v>
       </c>
       <c r="S383" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T383" s="2" t="s">
         <v>857</v>
@@ -26853,7 +26853,7 @@
         <v>856</v>
       </c>
       <c r="S384" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T384" s="2" t="s">
         <v>857</v>
@@ -26915,7 +26915,7 @@
         <v>856</v>
       </c>
       <c r="S385" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T385" s="2" t="s">
         <v>857</v>
@@ -26977,7 +26977,7 @@
         <v>856</v>
       </c>
       <c r="S386" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T386" s="2" t="s">
         <v>857</v>
@@ -27039,7 +27039,7 @@
         <v>856</v>
       </c>
       <c r="S387" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T387" s="2" t="s">
         <v>857</v>
@@ -27101,7 +27101,7 @@
         <v>856</v>
       </c>
       <c r="S388" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T388" s="2" t="s">
         <v>857</v>
@@ -27163,7 +27163,7 @@
         <v>856</v>
       </c>
       <c r="S389" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T389" s="2" t="s">
         <v>857</v>
@@ -27225,7 +27225,7 @@
         <v>856</v>
       </c>
       <c r="S390" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T390" s="2" t="s">
         <v>857</v>
@@ -27287,7 +27287,7 @@
         <v>856</v>
       </c>
       <c r="S391" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T391" s="2" t="s">
         <v>857</v>
@@ -27349,7 +27349,7 @@
         <v>856</v>
       </c>
       <c r="S392" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T392" s="2" t="s">
         <v>857</v>
@@ -27411,7 +27411,7 @@
         <v>856</v>
       </c>
       <c r="S393" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T393" s="2" t="s">
         <v>857</v>
@@ -27473,7 +27473,7 @@
         <v>856</v>
       </c>
       <c r="S394" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T394" s="2" t="s">
         <v>857</v>
@@ -27535,7 +27535,7 @@
         <v>856</v>
       </c>
       <c r="S395" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T395" s="2" t="s">
         <v>857</v>
@@ -27597,7 +27597,7 @@
         <v>856</v>
       </c>
       <c r="S396" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T396" s="2" t="s">
         <v>857</v>
@@ -27659,7 +27659,7 @@
         <v>856</v>
       </c>
       <c r="S397" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T397" s="2" t="s">
         <v>857</v>
@@ -27721,7 +27721,7 @@
         <v>856</v>
       </c>
       <c r="S398" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T398" s="2" t="s">
         <v>857</v>
@@ -27783,7 +27783,7 @@
         <v>856</v>
       </c>
       <c r="S399" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T399" s="2" t="s">
         <v>857</v>
@@ -27845,7 +27845,7 @@
         <v>856</v>
       </c>
       <c r="S400" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T400" s="2" t="s">
         <v>857</v>
@@ -27907,7 +27907,7 @@
         <v>856</v>
       </c>
       <c r="S401" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T401" s="2" t="s">
         <v>857</v>
@@ -27969,7 +27969,7 @@
         <v>856</v>
       </c>
       <c r="S402" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T402" s="2" t="s">
         <v>857</v>
@@ -28031,7 +28031,7 @@
         <v>856</v>
       </c>
       <c r="S403" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T403" s="2" t="s">
         <v>857</v>
@@ -28093,7 +28093,7 @@
         <v>856</v>
       </c>
       <c r="S404" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T404" s="2" t="s">
         <v>857</v>
@@ -28155,7 +28155,7 @@
         <v>856</v>
       </c>
       <c r="S405" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T405" s="2" t="s">
         <v>857</v>
@@ -28217,7 +28217,7 @@
         <v>856</v>
       </c>
       <c r="S406" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T406" s="2" t="s">
         <v>857</v>
@@ -28279,7 +28279,7 @@
         <v>856</v>
       </c>
       <c r="S407" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T407" s="2" t="s">
         <v>857</v>
@@ -28341,7 +28341,7 @@
         <v>856</v>
       </c>
       <c r="S408" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T408" s="2" t="s">
         <v>857</v>
@@ -28403,7 +28403,7 @@
         <v>856</v>
       </c>
       <c r="S409" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T409" s="2" t="s">
         <v>857</v>
@@ -28465,7 +28465,7 @@
         <v>856</v>
       </c>
       <c r="S410" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T410" s="2" t="s">
         <v>857</v>
@@ -28527,7 +28527,7 @@
         <v>856</v>
       </c>
       <c r="S411" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T411" s="2" t="s">
         <v>857</v>
@@ -28589,7 +28589,7 @@
         <v>856</v>
       </c>
       <c r="S412" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T412" s="2" t="s">
         <v>857</v>
@@ -28651,7 +28651,7 @@
         <v>856</v>
       </c>
       <c r="S413" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T413" s="2" t="s">
         <v>857</v>
@@ -28713,7 +28713,7 @@
         <v>856</v>
       </c>
       <c r="S414" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T414" s="2" t="s">
         <v>857</v>
@@ -28775,7 +28775,7 @@
         <v>856</v>
       </c>
       <c r="S415" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T415" s="2" t="s">
         <v>857</v>
@@ -28837,7 +28837,7 @@
         <v>856</v>
       </c>
       <c r="S416" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T416" s="2" t="s">
         <v>857</v>
@@ -28899,7 +28899,7 @@
         <v>856</v>
       </c>
       <c r="S417" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T417" s="2" t="s">
         <v>857</v>
@@ -28961,7 +28961,7 @@
         <v>856</v>
       </c>
       <c r="S418" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T418" s="2" t="s">
         <v>857</v>
@@ -29023,7 +29023,7 @@
         <v>856</v>
       </c>
       <c r="S419" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="T419" s="2" t="s">
         <v>857</v>
